--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -548,7 +548,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>62191.25</v>
+        <v>62013.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>29.97</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>2075.116783450117</v>
+        <v>2074.710605553697</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1307667310939524</v>
+        <v>0.1304918574927898</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0333667000333667</v>
+        <v>0.03345600535296086</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>72.30669243758096</v>
+        <v>72.19674299711592</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>58.28291682218337</v>
+        <v>58.24993199004386</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>25.35855471645671</v>
+        <v>25.35671699009465</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>52621.96249615745</v>
+        <v>52607.84966137299</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.1538687114962723</v>
+        <v>-0.1516655406458797</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>33.65999164394263</v>
+        <v>33.65907278076161</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>69848.41359113605</v>
+        <v>69832.83527134988</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1231228443090635</v>
+        <v>0.1260981191288595</v>
       </c>
     </row>
     <row r="15"/>
@@ -3834,7 +3834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3925,6 +3925,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>62013.1</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.477272727273</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.130491857493</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -547,8 +547,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>62013.1</v>
+        <v>61963.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>29.89</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>2074.710605553697</v>
+        <v>2075.122237106497</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1304918574927898</v>
+        <v>0.1308982251132775</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03345600535296086</v>
+        <v>0.03348961821835231</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>72.19674299711592</v>
+        <v>72.35929004531101</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>58.24993199004386</v>
+        <v>58.29869610450239</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>25.35671699009465</v>
+        <v>25.3594338479002</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>52607.84966137299</v>
+        <v>52623.92509820888</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.1516655406458797</v>
+        <v>-0.1507222422002613</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>33.65907278076161</v>
+        <v>33.6625872579863</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>69832.83527134988</v>
+        <v>69853.98337758519</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1260981191288595</v>
+        <v>0.1273471955119323</v>
       </c>
     </row>
     <row r="15"/>
@@ -3834,7 +3834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3958,6 +3958,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>61963.15</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.477272727273</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.130898225113</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>61963.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>29.86</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.4772727272727273</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>2075.122237106497</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.1308982251132775</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>52.27272727272727</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>72.35929004531101</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>58.29869610450239</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>25.3594338479002</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>52623.92509820888</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>-0.1507222422002613</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>33.6625872579863</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>69853.98337758519</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.1273471955119323</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.4086457258569968</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.2421637026205185</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.3243239617939847</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,19 +834,19 @@
       <c r="B19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.2385752782761117</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.2014612685267606</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.2025015332029516</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.1523382127242767</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,19 +859,19 @@
       <c r="B20" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.009356898367561817</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1759609886043725</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.2136464627626093</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="30" t="n">
         <v>0.1626918447310413</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -869,17 +884,17 @@
       <c r="B21" t="n">
         <v>6</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>-0.004410032845798828</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.2020587833118822</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1983569098779372</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,21 +907,20 @@
       <c r="B22" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.06463719335945262</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.273747258487266</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1803637341996653</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1042,16 +1056,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>24195.9</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>42.4</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1061,16 +1075,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>25775.45</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>37.83</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1080,16 +1094,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>26970.75</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>34.44</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1099,16 +1113,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>27815.25</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>34.49</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1118,16 +1132,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>28417.25</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>26.88</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1137,16 +1151,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>30384</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>32.02</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1156,16 +1170,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>30469.55</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>30.47</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1175,16 +1189,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>29650.65</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>27.96</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1194,16 +1208,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>30442.9</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>28.89</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1213,16 +1227,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>30273.95</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>28.75</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1232,16 +1246,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>28223.45</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>25.35</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1251,16 +1265,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>29692.3</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>25.43</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1270,16 +1284,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>29880.35</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>25.41</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1289,16 +1303,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>28288.35</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>21.83</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1308,16 +1322,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>26452.75</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>20.57</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1327,16 +1341,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>29634.25</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>22.42</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1346,16 +1360,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>31481.7</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>24.03</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1365,16 +1379,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>30668.3</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>22.81</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1384,16 +1398,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>31432.3</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>22.64</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1403,16 +1417,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>32037.9</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>24.68</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1422,16 +1436,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>31509.1</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>24.48</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1441,16 +1455,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>30676.45</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>23.5</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1460,16 +1474,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>30117.3</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>22.28</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1479,16 +1493,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>30035.15</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>21.68</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1498,16 +1512,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>31794.75</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>22.98</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1517,16 +1531,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>33761.3</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>23.17</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1536,16 +1550,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>35754.35</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>24.66</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1555,16 +1569,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>37721.35</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>25.42</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1574,16 +1588,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>39118.65</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>23.06</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1593,16 +1607,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>40537.05</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>25.1</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1612,16 +1626,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>38876.95</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>23.4</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1631,16 +1645,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>42908.9</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>22.99</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1650,16 +1664,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>46181.65</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>24.65</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1669,16 +1683,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>48568.6</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>25.78</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1688,16 +1702,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>48335.7</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>25.06</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1707,16 +1721,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>48075.75</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>32.89</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1726,16 +1740,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>50868.2</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>34.53</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1745,16 +1759,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>51705.7</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>38.97</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1764,16 +1778,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>55736.9</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>41.74</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1783,16 +1797,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>58990.9</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>45.41</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1802,16 +1816,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>59286.65</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>44.21</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1821,16 +1835,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>60153.8</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>44.95</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1840,16 +1854,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>56112.85</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>42.24</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1859,16 +1873,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>56392.65</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>41.3</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1878,16 +1892,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>57199.45</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>42.9</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1897,16 +1911,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>53712.2</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>37.98</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1916,16 +1930,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>47915.2</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>32.5</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1935,16 +1949,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>51672.25</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>32.49</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1954,16 +1968,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>54124.9</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>32.79</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1973,16 +1987,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>57420</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>32.84</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1992,16 +2006,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>59741.2</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>33.66</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2011,16 +2025,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>57400.55</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>31.95</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2030,16 +2044,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>55727.4</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>30.37</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2049,16 +2063,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>56529.3</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>32.7</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2068,16 +2082,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>59825.9</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>34.33</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2087,16 +2101,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>61043.25</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>33.63</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2106,16 +2120,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>60484.5</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>33.84</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2125,16 +2139,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>58432</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>32.07</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2144,16 +2158,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>59115.6</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>32.89</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2163,16 +2177,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>52650</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>32.55</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2182,16 +2196,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>59784.85</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>35.44</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2201,16 +2215,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>61723.8</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>29.76</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2220,16 +2234,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>61797.7</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>29.78</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2239,16 +2253,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>62915.3</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>31.35</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2258,16 +2272,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>64224.75</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>30.95</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2369,13 +2383,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>13396.7</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>27.43</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2383,12 +2397,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,C2)+1)/2)/COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2396,28 +2410,28 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16" t="n"/>
+      <c r="L2" s="30" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>12752.6</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>23.79</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2425,12 +2439,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,C3)+1)/2)/COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2438,28 +2452,28 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16" t="n"/>
+      <c r="L3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>18181.3</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>48.36</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2467,12 +2481,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,C4)+1)/2)/COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2480,28 +2494,28 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16" t="n"/>
+      <c r="L4" s="30" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>17154.35</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>47.19</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2509,12 +2523,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,C5)+1)/2)/COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2522,28 +2536,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>17875.5</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>42.29</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2551,15 +2565,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,C6)+1)/2)/COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2567,28 +2581,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>18258.5</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>33.81</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2596,15 +2610,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,C7)+1)/2)/COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2612,28 +2626,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>17654.1</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>30.96</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2641,15 +2655,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,C8)+1)/2)/COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2657,28 +2671,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>16026</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>23.7</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2686,15 +2700,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,C9)+1)/2)/COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2702,28 +2716,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>17102.5</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>24.95</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2731,15 +2745,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,C10)+1)/2)/COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2747,28 +2761,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>11703.75</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>17.47</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2776,15 +2790,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,C11)+1)/2)/COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2792,28 +2806,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>14704</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>88.29000000000001</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2821,15 +2835,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,C12)+1)/2)/COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2837,42 +2851,42 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>16983.05</v>
       </c>
-      <c r="C13" s="7" t="n"/>
+      <c r="C13" s="25" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,C13)+1)/2)/COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2880,28 +2894,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>20842.5</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>419.32</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2909,15 +2923,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,C14)+1)/2)/COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2925,28 +2939,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>23693.15</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>41.85</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2954,15 +2968,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,C15)+1)/2)/COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2970,28 +2984,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>26970.75</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>34.44</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2999,15 +3013,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,C16)+1)/2)/COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3015,28 +3029,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>30384</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>32.02</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3044,15 +3058,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,C17)+1)/2)/COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3060,25 +3074,25 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
+      <c r="K17" s="30" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>30442.9</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>28.89</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3086,15 +3100,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,C18)+1)/2)/COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3102,25 +3116,25 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
+      <c r="K18" s="30" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>29692.3</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>25.43</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3128,15 +3142,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,C19)+1)/2)/COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3144,25 +3158,25 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
+      <c r="K19" s="30" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>26452.75</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>20.57</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3170,15 +3184,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,C20)+1)/2)/COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3186,25 +3200,25 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
+      <c r="K20" s="30" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>30668.3</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>22.81</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3212,15 +3226,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,C21)+1)/2)/COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3228,25 +3242,25 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
+      <c r="K21" s="30" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>31509.1</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>24.48</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3254,15 +3268,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,C22)+1)/2)/COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3270,25 +3284,25 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
+      <c r="K22" s="30" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>30035.15</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>21.68</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3296,15 +3310,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,C23)+1)/2)/COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3312,25 +3326,25 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
+      <c r="K23" s="30" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>35754.35</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>24.66</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3338,15 +3352,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,C24)+1)/2)/COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3354,25 +3368,25 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>40537.05</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>25.1</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3380,15 +3394,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,C25)+1)/2)/COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3396,22 +3410,22 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="J25" s="30" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>46181.65</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>24.65</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3419,15 +3433,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,C26)+1)/2)/COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3435,22 +3449,22 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="J26" s="30" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>48075.75</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>32.89</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3458,15 +3472,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,C27)+1)/2)/COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3474,22 +3488,22 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>55736.9</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>41.74</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3497,15 +3511,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,C28)+1)/2)/COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3513,22 +3527,22 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="J28" s="30" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>60153.8</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>44.95</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3536,15 +3550,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,C29)+1)/2)/COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3552,22 +3566,22 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="J29" s="30" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>57199.45</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>42.9</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3575,15 +3589,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,C30)+1)/2)/COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3591,22 +3605,22 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>51672.25</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>32.49</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3614,15 +3628,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,C31)+1)/2)/COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3630,22 +3644,22 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>59741.2</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>33.66</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3653,15 +3667,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,C32)+1)/2)/COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3669,22 +3683,22 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="J32" s="30" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>56529.3</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>32.7</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3692,15 +3706,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,C33)+1)/2)/COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3708,19 +3722,19 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="I33" s="30" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>60484.5</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>33.84</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3728,15 +3742,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,C34)+1)/2)/COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3744,19 +3758,19 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="I34" s="30" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>52650</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>32.55</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3764,15 +3778,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,C35)+1)/2)/COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3780,19 +3794,19 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="I35" s="30" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>61797.7</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>29.78</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3800,15 +3814,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,C36)+1)/2)/COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3816,10 +3830,10 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="I36" s="30" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3896,30 +3910,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>62191.25</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>29.97</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.477272727273</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.130766731094</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -3929,30 +3943,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>62013.1</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>29.89</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.477272727273</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.130491857493</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -3962,30 +3976,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>61963.15</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>29.86</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.477272727273</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.130898225113</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4105,4 +4119,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Midcap 100 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4018,6 +4021,2112 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E105"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Midcap 100 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Adani Total Gas Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aditya Birla Capital Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alkem Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APL Apollo Tubes Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ashok Leyland Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Astral Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AU Small Finance Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bank of India</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BDL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bharat Forge Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bharat Heavy Electricals Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Billionbrains Garage Ventures Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Biocon Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Blue Star Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BSE Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cochin Shipyard Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>COCHINSHIP</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Coforge Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Colgate Palmolive (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Container Corporation of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Coromandel International Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COROMANDEL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dabur India Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Dixon Technologies (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Exide Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Federal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fortis Healthcare Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FSN E-Commerce Ventures Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GE Vernova T&amp;D India Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GMR Airports Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Godfrey Phillips India Ltd.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GODFRYPHLP</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Godrej Properties Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Havells India Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hitachi Energy India Ltd.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Housing &amp; Urban Development Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HUDCO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Asset Management Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ICICIAMC</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>IDFC First Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Indian Bank</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Indian Renewable Energy Development Agency Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>IREDA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Indus Towers Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IndusInd Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Info Edge (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JSW Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Jubilant Foodworks Ltd.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kalyan Jewellers India Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>KEI Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>KPIT Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>L&amp;T Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Laurus Labs Ltd.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Lenskart Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LG Electronics India Ltd.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>LGEINDIA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LIC Housing Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Lupin Ltd.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>M&amp;MFIN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mankind Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Marico Ltd.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Max Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Motilal Oswal Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MphasiS Ltd.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MRF Ltd.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Multi Commodity Exchange of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>National Aluminium Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NHPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NMDC Ltd.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Oberoi Realty Ltd.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Oil India Ltd.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>One 97 Communications Ltd.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ONE WAM Ltd.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Oracle Financial Services Software Ltd.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Page Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Textiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Patanjali Foods Ltd.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PB Fintech Ltd.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Persistent Systems Ltd.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Phoenix Mills Ltd.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PI Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Polycab India Ltd.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Premier Energies Ltd.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Prestige Estates Projects Ltd.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Radico Khaitan Ltd</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Rail Vikas Nigam Ltd.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SBI Cards and Payment Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SRF Ltd.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Steel Authority of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Supreme Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Suzlon Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Swiggy Ltd.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SWIGGY</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tata Communications Ltd.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tata Elxsi Ltd.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tata Investment Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TATAINVEST</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tube Investments of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>UPL Ltd.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Vishal Mega Mart Ltd.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Vodafone Idea Ltd.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Voltas Ltd.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Waaree Energies Ltd.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Yes Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4119,43 +6228,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Midcap 100 Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>61963.15</v>
+        <v>62396.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.86</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2075.122237106497</v>
+        <v>2075.039906883937</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1308982251132775</v>
+        <v>0.1308737983311838</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03348961821835231</v>
+        <v>0.03325573661456601</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.35929004531101</v>
+        <v>72.34951933247353</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>58.29869610450239</v>
+        <v>58.29576489065114</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.3594338479002</v>
+        <v>25.3592705374142</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>52623.92509820888</v>
+        <v>52621.49837460055</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1507222422002613</v>
+        <v>-0.1566587782702293</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>33.6625872579863</v>
+        <v>33.66209732652831</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>69853.98337758519</v>
+        <v>69850.19530195734</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1273471955119323</v>
+        <v>0.1194578425849122</v>
       </c>
     </row>
     <row r="16">
@@ -3851,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4008,6 +4008,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>62396.45</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.477272727273</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.130873798331</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>62396.45</v>
+        <v>60990.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>30.07</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.446969696969697</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2075.039906883937</v>
+        <v>2074.494897959184</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1308737983311838</v>
+        <v>0.1306417916539808</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03325573661456601</v>
+        <v>0.03401360544217687</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>52.27272727272727</v>
+        <v>55.3030303030303</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.34951933247353</v>
+        <v>72.25671666159232</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>58.29576489065114</v>
+        <v>60.3891362105989</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.3592705374142</v>
+        <v>25.35771940705805</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>52621.49837460055</v>
+        <v>52604.45953382249</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1566587782702293</v>
+        <v>-0.1374925371748965</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>33.66209732652831</v>
+        <v>33.65957398924331</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>69850.19530195734</v>
+        <v>69826.61450816489</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1194578425849122</v>
+        <v>0.1448834690218812</v>
       </c>
     </row>
     <row r="16">
@@ -3851,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4041,6 +4041,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>60990.15</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.44696969697</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.130641791654</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4081,7 +4114,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>60990.15</v>
+        <v>60906</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.4</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2074.494897959184</v>
+        <v>2075.161839863714</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1306417916539808</v>
+        <v>0.1306760088561914</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03401360544217687</v>
+        <v>0.03407155025553663</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.25671666159232</v>
+        <v>72.27040354247654</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>60.3891362105989</v>
+        <v>60.39324227486416</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.35771940705805</v>
+        <v>25.35794817349568</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>52604.45953382249</v>
+        <v>52621.84638688</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1374925371748965</v>
+        <v>-0.1360153944294488</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>33.65957398924331</v>
+        <v>33.65968837246212</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>69826.61450816489</v>
+        <v>69849.30085223775</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1448834690218812</v>
+        <v>0.1468377639680449</v>
       </c>
     </row>
     <row r="16">
@@ -3851,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4074,6 +4074,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>60906</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.44696969697</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.130676008856</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4114,7 +4147,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>60906</v>
+        <v>59914.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.35</v>
+        <v>28.88</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.446969696969697</v>
+        <v>0.4318181818181818</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2075.161839863714</v>
+        <v>2074.591412742382</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1306760088561914</v>
+        <v>0.1304201367265736</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03407155025553663</v>
+        <v>0.03462603878116344</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>55.3030303030303</v>
+        <v>56.81818181818181</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.27040354247654</v>
+        <v>72.16805469062943</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>60.39324227486416</v>
+        <v>61.42314367991609</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.35794817349568</v>
+        <v>25.35623748554338</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>52621.84638688</v>
+        <v>52603.83254696478</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1360153944294488</v>
+        <v>-0.1220139374811851</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>33.65968837246212</v>
+        <v>33.65883302848597</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>69849.30085223775</v>
+        <v>69828.32596382666</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1468377639680449</v>
+        <v>0.16547205777306</v>
       </c>
     </row>
     <row r="16">
@@ -3851,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4107,6 +4107,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>59914.2</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.431818181818</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.130420136727</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4147,7 +4180,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>59914.2</v>
+        <v>59319.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.88</v>
+        <v>28.59</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4318181818181818</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2074.591412742382</v>
+        <v>2074.830360265827</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1304201367265736</v>
+        <v>0.1307617459807235</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03462603878116344</v>
+        <v>0.03497726477789437</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>56.81818181818181</v>
+        <v>58.33333333333333</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.16805469062943</v>
+        <v>72.30469839228941</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>61.42314367991609</v>
+        <v>62.52474285102015</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.35623748554338</v>
+        <v>25.35852138741398</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>52603.83254696478</v>
+        <v>52614.63006605684</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1220139374811851</v>
+        <v>-0.1130282830565239</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>33.65883302848597</v>
+        <v>33.65997497942127</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>69828.32596382666</v>
+        <v>69838.73801309138</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.16547205777306</v>
+        <v>0.1773338572725176</v>
       </c>
     </row>
     <row r="16">
@@ -3851,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4140,6 +4140,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>59319.4</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.416666666667</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.130761745981</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4180,7 +4213,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4290,17 +4323,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Apar Industries Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4430,17 +4463,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bharat Dynamics Ltd.</t>
+          <t>Bank of Maharashtra</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4450,17 +4483,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bharat Forge Ltd.</t>
+          <t>Bharat Dynamics Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4470,17 +4503,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>Bharat Forge Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4490,17 +4523,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Billionbrains Garage Ventures Ltd.</t>
+          <t>Bharat Heavy Electricals Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GROWW</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4510,17 +4543,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Biocon Ltd.</t>
+          <t>Billionbrains Garage Ventures Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>GROWW</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4530,17 +4563,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Blue Star Ltd.</t>
+          <t>Biocon Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4550,17 +4583,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>Blue Star Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4650,17 +4683,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Dabur India Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4670,17 +4703,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dabur India Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4690,17 +4723,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>Exide Industries Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4710,17 +4743,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Exide Industries Ltd.</t>
+          <t>Federal Bank Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4730,17 +4763,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Federal Bank Ltd.</t>
+          <t>Fortis Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4750,17 +4783,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Ltd.</t>
+          <t>FSN E-Commerce Ventures Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -4770,17 +4803,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Ltd.</t>
+          <t>GE Vernova T&amp;D India Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4790,17 +4823,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D India Ltd.</t>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4810,17 +4843,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Glenmark Pharmaceuticals Ltd.</t>
+          <t>GMR Airports Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -4830,17 +4863,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GMR Airports Ltd.</t>
+          <t>Godfrey Phillips India Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>GODFRYPHLP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4850,17 +4883,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Godfrey Phillips India Ltd.</t>
+          <t>Godrej Properties Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GODFRYPHLP</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -4870,17 +4903,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Godrej Properties Ltd.</t>
+          <t>Havells India Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4890,17 +4923,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Havells India Ltd.</t>
+          <t>Hero MotoCorp Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4910,17 +4943,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hero MotoCorp Ltd.</t>
+          <t>Hindustan Copper Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -4950,17 +4983,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hitachi Energy India Ltd.</t>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4970,12 +5003,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Housing &amp; Urban Development Corporation Ltd.</t>
+          <t>ICICI Prudential Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HUDCO</t>
+          <t>ICICIAMC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4990,12 +5023,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5010,12 +5043,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ICICI Prudential Asset Management Company Ltd.</t>
+          <t>Indian Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ICICIAMC</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5030,17 +5063,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IDFC First Bank Ltd.</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5050,17 +5083,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5070,17 +5103,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+          <t>Indian Renewable Energy Development Agency Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5090,17 +5123,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Indian Renewable Energy Development Agency Ltd.</t>
+          <t>Indus Towers Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5143,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Indus Towers Ltd.</t>
+          <t>IndusInd Bank Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5130,17 +5163,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IndusInd Bank Ltd.</t>
+          <t>Info Edge (India) Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5150,17 +5183,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Info Edge (India) Ltd.</t>
+          <t>JSW Energy Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -5170,17 +5203,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JSW Energy Ltd.</t>
+          <t>Jubilant Foodworks Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5223,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jubilant Foodworks Ltd.</t>
+          <t>Kalyan Jewellers India Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5210,17 +5243,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kalyan Jewellers India Ltd.</t>
+          <t>KEI Industries Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5230,17 +5263,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KEI Industries Ltd.</t>
+          <t>L&amp;T Finance Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5250,17 +5283,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KPIT Technologies Ltd.</t>
+          <t>Laurus Labs Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5270,17 +5303,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Ltd.</t>
+          <t>Lenskart Solutions Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5290,17 +5323,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Laurus Labs Ltd.</t>
+          <t>LG Electronics India Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5310,17 +5343,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lenskart Solutions Ltd.</t>
+          <t>LIC Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5330,17 +5363,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LG Electronics India Ltd.</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5350,17 +5383,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LIC Housing Finance Ltd.</t>
+          <t>Lodha Developers Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -5470,17 +5503,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Ltd.</t>
+          <t>Meesho Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5490,17 +5523,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MphasiS Ltd.</t>
+          <t>Motilal Oswal Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5510,17 +5543,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MRF Ltd.</t>
+          <t>MphasiS Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5530,17 +5563,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Ltd.</t>
+          <t>MRF Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5550,17 +5583,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>National Aluminium Co. Ltd.</t>
+          <t>Multi Commodity Exchange of India Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5603,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NHPC Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5590,17 +5623,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NMDC Ltd.</t>
+          <t>NHPC Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -5610,17 +5643,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Oberoi Realty Ltd.</t>
+          <t>NLC India Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -5630,17 +5663,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Oil India Ltd.</t>
+          <t>NMDC Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5650,17 +5683,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>One 97 Communications Ltd.</t>
+          <t>Oberoi Realty Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -5670,17 +5703,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ONE WAM Ltd.</t>
+          <t>Oil India Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5690,17 +5723,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Ltd.</t>
+          <t>One 97 Communications Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5710,17 +5743,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Page Industries Ltd.</t>
+          <t>ONE WAM Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5730,17 +5763,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Patanjali Foods Ltd.</t>
+          <t>Oracle Financial Services Software Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5750,17 +5783,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PB Fintech Ltd.</t>
+          <t>Page Industries Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -5770,17 +5803,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Persistent Systems Ltd.</t>
+          <t>Patanjali Foods Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5790,17 +5823,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Phoenix Mills Ltd.</t>
+          <t>PB Fintech Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5810,17 +5843,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PI Industries Ltd.</t>
+          <t>Persistent Systems Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5830,17 +5863,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Polycab India Ltd.</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -5850,17 +5883,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Premier Energies Ltd.</t>
+          <t>PI Industries Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5870,17 +5903,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Prestige Estates Projects Ltd.</t>
+          <t>Premier Energies Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5890,17 +5923,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Radico Khaitan Ltd</t>
+          <t>Prestige Estates Projects Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -5910,17 +5943,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Rail Vikas Nigam Ltd.</t>
+          <t>Radico Khaitan Ltd</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5930,17 +5963,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>Rail Vikas Nigam Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -5950,17 +5983,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SRF Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5970,17 +6003,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Steel Authority of India Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5990,17 +6023,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>SRF Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6010,17 +6043,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Suzlon Energy Ltd.</t>
+          <t>Steel Authority of India Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6063,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Swiggy Ltd.</t>
+          <t>Supreme Industries Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6050,17 +6083,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tata Communications Ltd.</t>
+          <t>Suzlon Energy Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6070,17 +6103,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tata Elxsi Ltd.</t>
+          <t>Swiggy Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6090,17 +6123,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tata Investment Corporation Ltd.</t>
+          <t>Tata Communications Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -6130,17 +6163,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>UPL Ltd.</t>
+          <t>United Spirits Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -6150,17 +6183,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vishal Mega Mart Ltd.</t>
+          <t>UPL Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6170,17 +6203,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Vodafone Idea Ltd.</t>
+          <t>Vishal Mega Mart Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>59319.4</v>
+        <v>59332.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.59</v>
+        <v>27.98</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.417910447761194</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2074.830360265827</v>
+        <v>2120.51644031451</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1307617459807235</v>
+        <v>0.2266362328612683</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03497726477789437</v>
+        <v>0.03573981415296641</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>58.33333333333333</v>
+        <v>58.2089552238806</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.30469839228941</v>
+        <v>95.32724657225367</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>62.52474285102015</v>
+        <v>69.34444262839251</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.35852138741398</v>
+        <v>27.97927985203732</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>52614.63006605684</v>
+        <v>59330.52291440568</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1130282830565239</v>
+        <v>-2.573795434890336e-05</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>33.65997497942127</v>
+        <v>36.03679946131697</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>69838.73801309138</v>
+        <v>76416.62571403974</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1773338572725176</v>
+        <v>0.2879485154151884</v>
       </c>
     </row>
     <row r="16">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" s="30" t="n">
         <v>0.2385752782761117</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.2014612685267606</v>
+        <v>0.2000918181130569</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.2025015332029516</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="30" t="n">
         <v>0.009356898367561817</v>
@@ -869,7 +869,7 @@
         <v>0.1759609886043725</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>0.2136464627626093</v>
+        <v>0.1784320043584599</v>
       </c>
       <c r="F20" s="30" t="n">
         <v>0.1626918447310413</v>
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>-0.004410032845798828</v>
+        <v>0.03442347994348949</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>0.2020587833118822</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
@@ -971,7 +971,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2290,6 +2290,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>59332.05</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2306,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2406,7 +2425,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,C2)+1)/2)/COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,C2)+1)/2)/COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2448,7 +2467,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,C3)+1)/2)/COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,C3)+1)/2)/COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2490,7 +2509,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,C4)+1)/2)/COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,C4)+1)/2)/COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2532,7 +2551,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,C5)+1)/2)/COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,C5)+1)/2)/COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2577,7 +2596,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,C6)+1)/2)/COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,C6)+1)/2)/COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2622,7 +2641,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,C7)+1)/2)/COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,C7)+1)/2)/COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2667,7 +2686,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,C8)+1)/2)/COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,C8)+1)/2)/COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2712,7 +2731,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,C9)+1)/2)/COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,C9)+1)/2)/COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2757,7 +2776,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,C10)+1)/2)/COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,C10)+1)/2)/COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2802,7 +2821,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,C11)+1)/2)/COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,C11)+1)/2)/COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2847,7 +2866,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,C12)+1)/2)/COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,C12)+1)/2)/COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2890,7 +2909,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,C13)+1)/2)/COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,C13)+1)/2)/COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2935,7 +2954,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,C14)+1)/2)/COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,C14)+1)/2)/COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2980,7 +2999,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,C15)+1)/2)/COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,C15)+1)/2)/COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3025,7 +3044,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,C16)+1)/2)/COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,C16)+1)/2)/COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3070,7 +3089,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,C17)+1)/2)/COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,C17)+1)/2)/COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3085,7 +3104,10 @@
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="30" t="n"/>
+      <c r="K17" s="30">
+        <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
@@ -3112,7 +3134,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,C18)+1)/2)/COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,C18)+1)/2)/COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3154,7 +3176,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,C19)+1)/2)/COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,C19)+1)/2)/COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3196,7 +3218,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,C20)+1)/2)/COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,C20)+1)/2)/COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3238,7 +3260,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,C21)+1)/2)/COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,C21)+1)/2)/COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3280,7 +3302,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,C22)+1)/2)/COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,C22)+1)/2)/COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3322,7 +3344,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,C23)+1)/2)/COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,C23)+1)/2)/COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3364,7 +3386,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,C24)+1)/2)/COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,C24)+1)/2)/COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3406,7 +3428,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,C25)+1)/2)/COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,C25)+1)/2)/COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3417,7 +3439,10 @@
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="30" t="n"/>
+      <c r="J25" s="30">
+        <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K25" s="30" t="n"/>
       <c r="L25" s="30" t="n"/>
     </row>
@@ -3445,7 +3470,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,C26)+1)/2)/COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,C26)+1)/2)/COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3484,7 +3509,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,C27)+1)/2)/COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,C27)+1)/2)/COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3523,7 +3548,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,C28)+1)/2)/COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,C28)+1)/2)/COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3562,7 +3587,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,C29)+1)/2)/COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,C29)+1)/2)/COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3601,7 +3626,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,C30)+1)/2)/COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,C30)+1)/2)/COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3640,7 +3665,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,C31)+1)/2)/COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,C31)+1)/2)/COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3679,7 +3704,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,C32)+1)/2)/COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,C32)+1)/2)/COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3718,14 +3743,17 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,C33)+1)/2)/COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,C33)+1)/2)/COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="30" t="n"/>
+      <c r="I33" s="30">
+        <f>IFERROR(B37/B33-1,"")</f>
+        <v/>
+      </c>
       <c r="J33" s="30" t="n"/>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
@@ -3754,7 +3782,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,C34)+1)/2)/COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,C34)+1)/2)/COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3790,7 +3818,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,C35)+1)/2)/COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,C35)+1)/2)/COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3826,7 +3854,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,C36)+1)/2)/COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,C36)+1)/2)/COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3837,6 +3865,42 @@
       <c r="J36" s="30" t="n"/>
       <c r="K36" s="30" t="n"/>
       <c r="L36" s="30" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B37" s="24" t="n">
+        <v>59332.05</v>
+      </c>
+      <c r="C37" s="25" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E37" s="33">
+        <f>IFERROR(B37/C37,"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="30">
+        <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="30">
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,C37)+1)/2)/COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I37" s="30" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3851,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3859,7 +3923,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4173,6 +4237,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>59332.05</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.417910447761</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.226636232861</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4213,7 +4310,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>59332.05</v>
+        <v>58732</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.98</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.417910447761194</v>
+        <v>0.3955223880597015</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2120.51644031451</v>
+        <v>2120.28880866426</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2266362328612683</v>
+        <v>0.2261527749531786</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03573981415296641</v>
+        <v>0.03610108303249097</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>58.2089552238806</v>
+        <v>60.44776119402986</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.32724657225367</v>
+        <v>95.23055499063574</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>69.34444262839251</v>
+        <v>70.88259933301163</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.97927985203732</v>
+        <v>27.94352710131133</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59330.52291440568</v>
+        <v>59248.34778751685</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-2.573795434890336e-05</v>
+        <v>0.008791592105102053</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.03679946131697</v>
+        <v>35.97143318952664</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>76416.62571403974</v>
+        <v>76269.82722336747</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2879485154151884</v>
+        <v>0.298607696372803</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4270,6 +4270,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>58732</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.226152774953</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4310,7 +4343,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>58732</v>
+        <v>59123.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.7</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2120.28880866426</v>
+        <v>2120.647417503587</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2261527749531786</v>
+        <v>0.2265847660383142</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03610108303249097</v>
+        <v>0.03586800573888092</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.23055499063574</v>
+        <v>95.31695320766285</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.88259933301163</v>
+        <v>70.90851879811976</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.94352710131133</v>
+        <v>27.9568864840134</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59248.34778751685</v>
+        <v>59286.69912376394</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.008791592105102053</v>
+        <v>0.002757764849834921</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.97143318952664</v>
+        <v>36.02984085275745</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>76269.82722336747</v>
+        <v>76406.58895746531</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.298607696372803</v>
+        <v>0.2923185384776703</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4303,6 +4303,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>59123.65</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.226584766038</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4343,7 +4376,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>59123.65</v>
+        <v>59761.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.88</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3955223880597015</v>
+        <v>0.4253731343283582</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2120.647417503587</v>
+        <v>2119.943242284498</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2265847660383142</v>
+        <v>0.2259583415118633</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03586800573888092</v>
+        <v>0.0354735721887194</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>60.44776119402986</v>
+        <v>57.46268656716418</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.31695320766285</v>
+        <v>95.19166830237268</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.90851879811976</v>
+        <v>68.78138108772671</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.9568864840134</v>
+        <v>27.97851286639628</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59286.69912376394</v>
+        <v>59312.85928028667</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.002757764849834921</v>
+        <v>-0.007502204100876986</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.02984085275745</v>
+        <v>35.94514467721255</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>76406.58895746531</v>
+        <v>76201.66655139533</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2923185384776703</v>
+        <v>0.2751026845410625</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4336,6 +4336,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>59761.2</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.425373134328</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.225958341512</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4376,7 +4409,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>59761.2</v>
+        <v>59382.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.19</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2119.943242284498</v>
+        <v>2120.049982149232</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2259583415118633</v>
+        <v>0.2260700041216861</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0354735721887194</v>
+        <v>0.03570153516601213</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.19166830237268</v>
+        <v>95.21400082433722</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>68.78138108772671</v>
+        <v>68.78808084431608</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.97851286639628</v>
+        <v>27.97863920466339</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59312.85928028667</v>
+        <v>59316.11354640643</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.007502204100876986</v>
+        <v>-0.001119628537544215</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.94514467721255</v>
+        <v>35.96024210013265</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>76201.66655139533</v>
+        <v>76237.51062246828</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2751026845410625</v>
+        <v>0.2838358479161958</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4369,6 +4369,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>59382.6</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.425373134328</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.226070004122</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4409,7 +4442,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>59382.6</v>
+        <v>57882.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.01</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4253731343283582</v>
+        <v>0.3955223880597015</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2120.049982149232</v>
+        <v>2120.238095238095</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2260700041216861</v>
+        <v>0.2263410170368827</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03570153516601213</v>
+        <v>0.03663003663003663</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>57.46268656716418</v>
+        <v>60.44776119402986</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.21400082433722</v>
+        <v>95.26820340737655</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>68.78808084431608</v>
+        <v>70.89389385803386</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.97863920466339</v>
+        <v>27.9252126018228</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59316.11354640643</v>
+        <v>59208.09957600763</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.001119628537544215</v>
+        <v>0.02290156050632963</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.96024210013265</v>
+        <v>35.99688459491247</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>76237.51062246828</v>
+        <v>76321.96602802274</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2838358479161958</v>
+        <v>0.318567201278845</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4402,6 +4402,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>57882.5</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.226341017037</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4442,7 +4475,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>57882.5</v>
+        <v>58787.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.3</v>
+        <v>27.73</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2120.238095238095</v>
+        <v>2119.989181391994</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2263410170368827</v>
+        <v>0.2259903874344276</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03663003663003663</v>
+        <v>0.03606202668589974</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.26820340737655</v>
+        <v>95.19807748688551</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.89389385803386</v>
+        <v>70.87285608188655</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.9252126018228</v>
+        <v>27.94331492678966</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59208.09957600763</v>
+        <v>59239.52533702352</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02290156050632963</v>
+        <v>0.007692568582389647</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.99688459491247</v>
+        <v>35.9494774690628</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>76321.96602802274</v>
+        <v>76212.50331110839</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.318567201278845</v>
+        <v>0.2964110158334945</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4435,6 +4435,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>58787.3</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.225990387434</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4475,7 +4508,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>58787.3</v>
+        <v>58834.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.73</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2119.989181391994</v>
+        <v>2120.163963963964</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2259903874344276</v>
+        <v>0.2262820257213536</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03606202668589974</v>
+        <v>0.03603603603603604</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.19807748688551</v>
+        <v>95.25640514427072</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.87285608188655</v>
+        <v>70.89035437910211</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.94331492678966</v>
+        <v>27.94823046556968</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59239.52533702352</v>
+        <v>59254.83108966063</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.007692568582389647</v>
+        <v>0.007143440200709117</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.9494774690628</v>
+        <v>35.9889086319597</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>76212.50331110839</v>
+        <v>76302.3871838726</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2964110158334945</v>
+        <v>0.2968976083589081</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4468,6 +4468,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>58834.55</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.226282025721</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4508,7 +4541,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>58834.55</v>
+        <v>59459.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.75</v>
+        <v>28.04</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3955223880597015</v>
+        <v>0.4253731343283582</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2120.163963963964</v>
+        <v>2120.513552068473</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2262820257213536</v>
+        <v>0.2269329046630724</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03603603603603604</v>
+        <v>0.03566333808844508</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>60.44776119402986</v>
+        <v>57.46268656716418</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.25640514427072</v>
+        <v>95.38658093261448</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.89035437910211</v>
+        <v>68.83985487679927</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.94823046556968</v>
+        <v>27.97961551499022</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59254.83108966063</v>
+        <v>59331.15388120209</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.007143440200709117</v>
+        <v>-0.002153512304200356</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.9889086319597</v>
+        <v>36.07691118418832</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>76302.3871838726</v>
+        <v>76501.57908284201</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2968976083589081</v>
+        <v>0.2866230807485135</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4501,6 +4501,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>59459.2</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.425373134328</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.226932904663</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4541,7 +4574,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>59459.2</v>
+        <v>59409.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.04</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2120.513552068473</v>
+        <v>2120.239114917916</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2269329046630724</v>
+        <v>0.2268976642448042</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03566333808844508</v>
+        <v>0.03568879371877231</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.38658093261448</v>
+        <v>95.37953284896084</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>68.83985487679927</v>
+        <v>68.83774045170317</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.97961551499022</v>
+        <v>27.97957564297412</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59331.15388120209</v>
+        <v>59323.39069703833</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.002153512304200356</v>
+        <v>-0.001442696539110555</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.07691118418832</v>
+        <v>36.07214647826464</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>76501.57908284201</v>
+        <v>76481.57592226521</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2866230807485135</v>
+        <v>0.2873713946561254</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4534,6 +4534,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>59409.1</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.425373134328</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.226897664245</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4574,7 +4607,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>59409.1</v>
+        <v>59197.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.02</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4253731343283582</v>
+        <v>0.3955223880597015</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2120.239114917916</v>
+        <v>2126.338002873563</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2268976642448042</v>
+        <v>0.2328217113489424</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03568879371877231</v>
+        <v>0.03591954022988506</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>57.46268656716418</v>
+        <v>60.44776119402986</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.37953284896084</v>
+        <v>96.56434226978847</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>68.83774045170317</v>
+        <v>71.28273551675744</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.97957564297412</v>
+        <v>27.96627827912623</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59323.39069703833</v>
+        <v>59465.76030384358</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.001442696539110555</v>
+        <v>0.004535857727235415</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.07214647826464</v>
+        <v>36.87311149844187</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>76481.57592226521</v>
+        <v>78404.6982633311</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2873713946561254</v>
+        <v>0.3244652118693199</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4567,6 +4567,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>59197.25</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.232821711349</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4607,7 +4640,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>59197.25</v>
+        <v>59129.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.84</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2126.338002873563</v>
+        <v>2129.267194814548</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2328217113489424</v>
+        <v>0.2335420586203221</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03591954022988506</v>
+        <v>0.03601008282319049</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>96.56434226978847</v>
+        <v>96.70841172406442</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.28273551675744</v>
+        <v>71.32595635304023</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.96627827912623</v>
+        <v>27.96709330061042</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59465.76030384358</v>
+        <v>59549.41429930749</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.004535857727235415</v>
+        <v>0.007097346078877242</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.87311149844187</v>
+        <v>36.97050656580253</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>78404.6982633311</v>
+        <v>78720.08680623918</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3244652118693199</v>
+        <v>0.331311003449857</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4600,6 +4600,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>59129.75</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.23354205862</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4640,7 +4673,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>59129.75</v>
+        <v>58487.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.77</v>
+        <v>27.35</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2129.267194814548</v>
+        <v>2138.499085923218</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2335420586203221</v>
+        <v>0.2376680659757904</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03601008282319049</v>
+        <v>0.03656307129798903</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>96.70841172406442</v>
+        <v>97.53361319515807</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.32595635304023</v>
+        <v>71.57351679436832</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.96709330061042</v>
+        <v>27.97176158321832</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59549.41429930749</v>
+        <v>59817.58657737456</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.007097346078877242</v>
+        <v>0.02273351309756211</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.97050656580253</v>
+        <v>37.52836633744671</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>78720.08680623918</v>
+        <v>80254.37710882144</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.331311003449857</v>
+        <v>0.3721523340931157</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4633,6 +4633,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>58487.95</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.237668065976</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4673,7 +4706,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>58487.95</v>
+        <v>57565.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.35</v>
+        <v>26.91</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2138.499085923218</v>
+        <v>2139.199182460052</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2376680659757904</v>
+        <v>0.2498260569754929</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03656307129798903</v>
+        <v>0.03716090672612412</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>97.53361319515807</v>
+        <v>99.96521139509858</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.57351679436832</v>
+        <v>72.30299625435046</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.97176158321832</v>
+        <v>28.19242304185247</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59817.58657737456</v>
+        <v>60309.20832269872</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02273351309756211</v>
+        <v>0.04765600304171169</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.52836633744671</v>
+        <v>37.91423825490632</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>80254.37710882144</v>
+        <v>81106.10747849123</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3721523340931157</v>
+        <v>0.4089274713826208</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4666,6 +4666,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>57565.85</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.249826056975</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4706,7 +4739,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>57565.85</v>
+        <v>57063.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.91</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3955223880597015</v>
+        <v>0.3805970149253731</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2139.199182460052</v>
+        <v>2142.844536237326</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2498260569754929</v>
+        <v>0.2519558531043846</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03716090672612412</v>
+        <v>0.03755163349605708</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>60.44776119402986</v>
+        <v>61.94029850746269</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>99.96521139509858</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.30299625435046</v>
+        <v>73.35820895522389</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.19242304185247</v>
+        <v>28.2</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>60309.20832269872</v>
+        <v>60428.2159218926</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04765600304171169</v>
+        <v>0.05895606458880964</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.91423825490632</v>
+        <v>37.91571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>81106.10747849123</v>
+        <v>81247.48119467839</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4089274713826208</v>
+        <v>0.4237970065983583</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4699,6 +4699,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>57063.95</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.251955853104</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4739,7 +4772,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>57063.95</v>
+        <v>55800.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.63</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2142.844536237326</v>
+        <v>2147.831023864511</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2519558531043846</v>
+        <v>0.2549551882074217</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03755163349605708</v>
+        <v>0.03849114703618168</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.2</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>60428.2159218926</v>
+        <v>60568.83487297922</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05895606458880964</v>
+        <v>0.08545034642032334</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>37.91571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>81247.48119467839</v>
+        <v>81436.54743483997</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4237970065983583</v>
+        <v>0.4594193335532823</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4732,6 +4732,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>55800.65</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.254955188207</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4772,7 +4805,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>55800.65</v>
+        <v>56465.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.98</v>
+        <v>26.28</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2147.831023864511</v>
+        <v>2148.607305936073</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2549551882074217</v>
+        <v>0.2558378849577054</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03849114703618168</v>
+        <v>0.0380517503805175</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.2</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>60568.83487297922</v>
+        <v>60590.72602739725</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.08545034642032334</v>
+        <v>0.07305936073059338</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>37.91571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>81436.54743483997</v>
+        <v>81465.98072407042</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4594193335532823</v>
+        <v>0.4427592954990209</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4765,6 +4765,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>56465.4</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.255837884958</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4805,7 +4838,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>56465.4</v>
+        <v>57029.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.28</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2148.607305936073</v>
+        <v>2195.146266358738</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2558378849577054</v>
+        <v>0.2819063879662984</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0380517503805175</v>
+        <v>0.03849114703618168</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.2</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>60590.72602739725</v>
+        <v>61903.1247113164</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07305936073059338</v>
+        <v>0.08545034642032334</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>37.91571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>81465.98072407042</v>
+        <v>83230.53865061035</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4427592954990209</v>
+        <v>0.4594193335532826</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4798,6 +4798,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>57029.9</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.281906387966</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4838,7 +4871,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>57029.9</v>
+        <v>57274.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.98</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2195.146266358738</v>
+        <v>2196.958189489835</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2819063879662984</v>
+        <v>0.2818118201852837</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03849114703618168</v>
+        <v>0.03835826620636747</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.2</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>61903.1247113164</v>
+        <v>61954.22094361335</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.08545034642032334</v>
+        <v>0.08170310701956285</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>37.91571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>83230.53865061035</v>
+        <v>83299.23901035672</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4594193335532826</v>
+        <v>0.4543810619759985</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4831,6 +4831,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>57274.7</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.281811820185</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4871,7 +4904,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>57274.7</v>
+        <v>57841.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.07</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2196.958189489835</v>
+        <v>2195.962414578588</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2818118201852837</v>
+        <v>0.2821848391620483</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03835826620636747</v>
+        <v>0.03796507213363706</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.2</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>61954.22094361335</v>
+        <v>61926.14009111618</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.08170310701956285</v>
+        <v>0.07061503416856496</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>37.91571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>83299.23901035672</v>
+        <v>83261.48349332898</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4543810619759985</v>
+        <v>0.4394728278555156</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4864,6 +4864,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>57841.65</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.282184839162</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4904,7 +4937,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-100.xlsx
+++ b/docs/downloads/indices/nifty-midcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>57841.65</v>
+        <v>57301.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.34</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2195.962414578588</v>
+        <v>2221.839860411012</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2821848391620483</v>
+        <v>0.297324886358507</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03796507213363706</v>
+        <v>0.0387747188832881</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.2</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>61926.14009111618</v>
+        <v>62655.88406359054</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07061503416856496</v>
+        <v>0.09344707250872419</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>37.91571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>83261.48349332898</v>
+        <v>84242.64533595523</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4394728278555156</v>
+        <v>0.4701711626876417</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4897,6 +4897,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>57301.25</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.297324886359</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4937,7 +4970,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
